--- a/main/04图片素材库/原始扫描图/秦简表.xlsx
+++ b/main/04图片素材库/原始扫描图/秦简表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="11655"/>
+    <workbookView windowWidth="21000" windowHeight="11055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="322">
   <si>
     <t>ID</t>
   </si>
@@ -617,6 +617,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>廿年：秦王政二十年（公元前 227 年）</t>
     </r>
     <r>
@@ -638,6 +646,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">圣王制定法度，用来匡正百姓的心志，去除邪恶乖僻的行为，革除恶劣的风俗。 早期法律尚不完备，百姓多有诡诈取巧，所以后来会出现扰乱、违抗法令的情况。 </t>
     </r>
     <r>
@@ -670,6 +685,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>（法律的作用，是）去除放纵邪僻的行为，革除恶劣风俗，使百姓能够向善。 如今法律政令已经完备，可是官吏、百姓并不遵行；固守地方旧俗、放纵放荡的人依然没有止息。</t>
     </r>
     <r>
@@ -696,6 +718,690 @@
   </si>
   <si>
     <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J3</t>
+  </si>
+  <si>
+    <t>J4语书</t>
+  </si>
+  <si>
+    <t>句首 “明法也” 承接上句 “是即废主之明法也”，指出：若基层官吏不推行法令、纵容不良风气，本质就是废弃君主确立的严明法度。点明放任 “邪僻淫泆”（品行不端、放纵越轨）的民间风气，会严重损害国家统治秩序，也不利于基层百姓的安定治理。说明南郡郡守腾针对这一问题，专门整饬（修）法律政令、农田管理专项法令（田令），以及惩处奸私违法行为的条规；将这些规范正式下达，要求基层官吏必须明确公布、宣讲给全体吏民知晓。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J4</t>
+  </si>
+  <si>
+    <t>J5语书</t>
+  </si>
+  <si>
+    <t>命令官吏、百姓全都清楚了解法令，不要触犯而陷入犯罪。 承接上简：郡守下令把法令、田令、惩治奸私的条文公布，让全体吏民知晓，避免无意犯法获罪。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J5</t>
+  </si>
+  <si>
+    <t>J6语书</t>
+  </si>
+  <si>
+    <t>知情却包庇放纵罪犯，属于不忠；不知情是能力不配岗位；知情却不敢查办，属于为官不廉。 郡守腾指出这两类都是重罪，批评南郡各县长官对此疏于监察，造成地方治理混乱，为后文宣布要派人巡视、追责县级官吏做铺垫。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J6</t>
+  </si>
+  <si>
+    <t>J7语书</t>
+  </si>
+  <si>
+    <t>J7 简就公布郡守的处置手段：派遣人员巡察地方，弹劾违法者，并且要连带追责县令、县丞，把对官吏的批评落到实际监察、问责制度上，以此督促南郡属县严格推行秦法，改造旧乡俗</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J7</t>
+  </si>
+  <si>
+    <t>J8语书</t>
+  </si>
+  <si>
+    <t>实行官吏连带追责：下面人犯法，主管的县令、县丞要一同承担罪责；通过考核，把地方案件多少作为评判主官政绩的依据。规定文告流转、公布的行政程序：文书逐级传递，在江陵公开张贴，依靠邮驿送达，保障郡守的政令在整个南郡落地推行。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J8</t>
+  </si>
+  <si>
+    <t>J9语书</t>
+  </si>
+  <si>
+    <t>大凡优秀的官吏，通晓法律政令，没有办不好的公务；又廉洁清白、忠厚谨慎，乐于辅佐上级。 懂得一个部门的公务，不能凭个人独断处置，所以怀有公正之心；又能够自我端正约束。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J9</t>
+  </si>
+  <si>
+    <t>J10语书</t>
+  </si>
+  <si>
+    <t>（良吏）能够自我端正，不喜欢独断专行处置公务，所以不会在文书事务上争执扯皮。 恶吏则不通晓法律政令，不懂处理公务，不廉洁清白，不能够辅佐上级；苟且懈怠，厌烦处理政务，喜好搬弄口舌。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J10</t>
+  </si>
+  <si>
+    <t>J11语书</t>
+  </si>
+  <si>
+    <t>（恶吏）搬弄口舌，不知羞耻，动辄出口恶语伤害他人。没有公正正直的本心，办事蛮横无理。所以爱挑起申诉事端，喜好在文书公务上争执。发生文书争执的时候，就佯装发怒，瞪起双眼，握住手腕</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J11</t>
+  </si>
+  <si>
+    <t>J12语书</t>
+  </si>
+  <si>
+    <t>（恶吏）握着手腕来炫耀威势；说话高声急促，以此装作善于处理公务；满口粗野恶语，以此显示自己凶狠；态度傲慢强横，以此表现自己强悍。可是上级竟然还赏识、认为这种人很能干。所以像这样的官吏，就不能</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J12</t>
+  </si>
+  <si>
+    <t>J13语书</t>
+  </si>
+  <si>
+    <t>（这类恶吏）不能不加以惩处。下发检举的文书，移送各官署部门；如果官署不肯受理，就要上报郡府。郡府命令相关部门登记标记官吏劣迹。劣迹登记最多的官吏，由其所属部门上报县令、县丞，认定其办事不公正，记录</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J13</t>
+  </si>
+  <si>
+    <t>J14语书</t>
+  </si>
+  <si>
+    <t>（认定官吏）不公正，流放千里之外，将此事记入官方档案，正式把他定为恶吏。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J14</t>
+  </si>
+  <si>
+    <t>秦律十八种J1</t>
+  </si>
+  <si>
+    <t>如降下及时雨，或是谷物抽穗，就要立刻用书面形式向上报告：受及时雨润泽的田地、谷物抽穗的田地，还有已经开垦却尚未种植庄稼的田地，各有多少顷。庄稼出苗生长之后下雨，也要随即上报雨量大小，以及雨水惠及的田地</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J1</t>
+  </si>
+  <si>
+    <t>秦律十八种J2</t>
+  </si>
+  <si>
+    <t>雨水惠及的田地顷数。如果发生旱灾、狂风暴雨、洪涝、蝗虫以及其他虫害伤害庄稼，也要马上书面上报受灾田地的顷数。邻近的县，派快跑差役递送这份报告；距离</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J2</t>
+  </si>
+  <si>
+    <t>秦律十八种J3</t>
+  </si>
+  <si>
+    <t>距离远的县由驿站递送报告，所有文书必须在八月底之前上报完毕</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J3</t>
+  </si>
+  <si>
+    <t>秦律十八种J4</t>
+  </si>
+  <si>
+    <t>春季三月，不准砍伐山林树木，不准堵塞水源泉流。夏季，不许焚烧野草做灰肥；不许采摘新生嫩芽，不许捕捉幼兽、鸟卵、雏鸟，不许......</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J4</t>
+  </si>
+  <si>
+    <t>秦律十八种J5</t>
+  </si>
+  <si>
+    <t>不许投毒捕杀鱼鳖，不许布设陷阱罗网捕猎；到七月，方才解除以上禁令。只有家中有丧事，砍伐木料打造棺椁的，可以不受这条时节禁令的限制。居住城邑靠近官家养马牛棚以及其他官设禁苑的地方，幼兽繁育时节……</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J5</t>
+  </si>
+  <si>
+    <t>秦律十八种J6</t>
+  </si>
+  <si>
+    <t>幼兽繁育的时节，不许带着猎犬前去狩猎。百姓家的狗闯入禁苑，如果不去追逐、捕捉苑中的野兽，就不可以捕杀这条狗；如果这条狗追逐、捕捉野兽，就可以把狗打死……</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J6</t>
+  </si>
+  <si>
+    <t>秦律十八种J7</t>
+  </si>
+  <si>
+    <t>在警戒禁区内打死的狗，必须完整上交官府；在其余普通禁苑中打死的狗，可以食用狗肉，但要把狗皮上缴官府。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J7</t>
+  </si>
+  <si>
+    <t>秦律十八种J8</t>
+  </si>
+  <si>
+    <t>缴纳每顷田地的刍、稾税，按照官府授田的数量来征收；无论土地开垦与否，每顷都要交刍三石、稾二石。干草、乱草，只要能够捆成束的，官府全部接收。缴纳刍稾，可以互相运送……</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J8</t>
+  </si>
+  <si>
+    <t>秦律十八种J9</t>
+  </si>
+  <si>
+    <t>缴纳刍、稾，可以互相运送、集中称量，这是准许的。【田律】</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J9</t>
+  </si>
+  <si>
+    <t>秦律十八种J10</t>
+  </si>
+  <si>
+    <t>谷物、刍稾草料出库，撤下仓库防潮所用的木架和草垫，必须马上将出库的粮草石数上报县府。这些木架、草垫不得挪作别的用途，依旧用来垫盖仓内存放的粮草。【田律】。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J10</t>
+  </si>
+  <si>
+    <t>秦律十八种J11</t>
+  </si>
+  <si>
+    <t>官府驾车服役牛马的饲料，如果超过两个月还没有领取，官府也没有下发送达，就一律停止，不再发放饲料。向大田申领饲料、又没有固定登记账簿的，要按照领取凭证送达的那一天才予以发放，发放数量不可以超过凭证的规定。【田律</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J11</t>
+  </si>
+  <si>
+    <t>秦律十八种J12</t>
+  </si>
+  <si>
+    <t>居住在乡间农舍的百姓，不许售卖酒。田啬夫、部佐要严格查禁这件事；有违反法令的，就要治罪。【田律】抖音百科</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J12</t>
+  </si>
+  <si>
+    <t>秦律十八种J13</t>
+  </si>
+  <si>
+    <t>在每年四月、七月、十月、正月，对耕田官牛进行检查评比。到年终，正月开展年度总考核。成绩最优的，赏赐田啬夫一壶酒、一束干肉；饲养牛的皂吏免除一次更役，赏赐牛长三十天劳绩；考核成绩最差的……</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J13</t>
+  </si>
+  <si>
+    <t>秦律十八种J14</t>
+  </si>
+  <si>
+    <t>考核成绩列为末等的，要斥责田啬夫，罚长期饲牛的皂隶两个月劳绩。如果使用官牛耕田，牛的腰围变瘦，每瘦一寸，笞罚主管人员十下。还要在里一级开展耕牛考核：成绩最优的，赏赐田典十天劳绩；成绩最差的，笞打三十下。【厩苑律】</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J14</t>
+  </si>
+  <si>
+    <t>秦律十八种J15</t>
+  </si>
+  <si>
+    <t>借用官府的铁制器具，如果因为使用磨损、破旧不堪使用而损坏，就开具损耗文书上报，官府收回破损器物，不追究借用人的赔偿责任。【厩苑律】。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J15</t>
+  </si>
+  <si>
+    <t>秦律十八种J16</t>
+  </si>
+  <si>
+    <t>率领放牧官有的牛马，如果牛马死亡，要立刻向死亡发生地的县上报；该县要马上检验，把死的牛马收归官府。如果没有及时上报收纳，致使尸体腐烂，就要按尸体未腐烂时的价值赔偿。如果未成年刑徒小隶臣因病死亡，按规定上报处理；倘若不是病死，就要拿着检验报告上报官府判罪。若是大厩、中厩、宫厩的牛马，要把筋、皮、角以及变卖所得的钱款核验上交，由放牧人员送交主管官府……</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J16</t>
+  </si>
+  <si>
+    <t>秦律十八种J17</t>
+  </si>
+  <si>
+    <t>（小隶臣）如果是因病死亡，按规定上报处置；如果不是病死，就要把勘验文书上交官府，依法论罪。若是大厩、中厩、宫厩这些宫廷马厩的牛马，要把（牛马的）筋、皮、角，连同变卖得到的价钱……</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J17</t>
+  </si>
+  <si>
+    <t>秦律十八种J18</t>
+  </si>
+  <si>
+    <t>驾乘官府的牛马，牛马在某个县死亡，该县要检验，把肉一起卖掉；筋、皮、角要上交，卖得的钱也要全部上缴。如果卖的钱达不到法定估价，就责令使用牛马的人补齐，上报官府；官府再通知牛马原登记县，注销该牛马的记录。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J18</t>
+  </si>
+  <si>
+    <t>秦律十八种J19</t>
+  </si>
+  <si>
+    <t>卖得的钱少于法律规定的估价，责令使用牛马的人补齐，上报官府；官府通知牛马原登记的县，把这头牛马从官畜档案中注销。现在对各县、都官的官役牛每年进行一次考核：满一年，饲养十头牛以上，死亡达到三分之一；或者饲养不到十头牛，一年死掉三头以上，主管官吏、饲养牛的役徒，以及县令、县丞都要论罪。内史考核各县，太仓考核都官以及领受官牛的单位。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J19</t>
+  </si>
+  <si>
+    <t>秦律十八种J20</t>
+  </si>
+  <si>
+    <t>谷物存入粮仓，一万石作为一积，用荆笆隔开，设置仓门。县啬夫或者县丞，以及仓、乡的官吏共同给粮仓加封；另外留给仓啬夫以及乡邑掌管发放粮食的仓佐一处仓门，用来发放口粮，由他们自行封印；就从这一门支取粮食，等到该仓粮食全部耗尽，再开启另一仓的仓门。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J20</t>
+  </si>
+  <si>
+    <t>秦律十八种J21</t>
+  </si>
+  <si>
+    <t>谷物存入粮仓，一万石作为一积，用荆笆隔开粮堆，设置仓门。由县啬夫或县丞，以及仓、乡的官吏共同给粮仓加封。另外留给仓啬夫以及乡邑掌管发放口粮的仓佐一处仓门，用来发放口粮，由他们自行封印；由此门支取粮食，待到该仓粮食全部用尽，再开启另一仓的仓门。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J21</t>
+  </si>
+  <si>
+    <t>秦律十八种J22</t>
+  </si>
+  <si>
+    <t>粮食入官仓，一万石为一个储粮单元，用荆笆隔开，分设仓门。县啬夫、县丞会同仓库、乡的官吏共同对粮仓封缄。专门留给仓啬夫、乡邑负责发放粮食的仓佐，单独一个仓门用于发放口粮（餼，廪给粮食），由他们自己封印；这一部分粮食可以直接出库使用。等到这一仓粮食全部发放耗尽，再开启另外的仓门。如果仓啬夫免职，就要对粮仓进行审计核验。核验人员开仓，看到多方共同封缄的仓，只核对封题标记，不需要称量；只有仓官自己单独封印的那一部分粮仓，才需要称量校验。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J22</t>
+  </si>
+  <si>
+    <t>秦律十八种J23</t>
+  </si>
+  <si>
+    <t>官吏离任核验规则（承接 J22）：多方官吏共同封缄（杂封）的粮仓，核验的时候不需要重新称量粮食；只有仓官自己单独封印的粮仓，才必须称量核验。粮食出库制度：出库粮食时，如果不是当初负责入仓的那批官吏来办理出库，就必须对粮食进行称量。称量结果要和粮仓标签（题，写有粮食数量的标牌）上记载的数目相符，才准许出库。责任追究：如果出库称量发现粮食数量不足，办理出库的官吏要赔偿补足亏欠的粮食；如果称量多出粮食，多出部分要归入官仓。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J23</t>
+  </si>
+  <si>
+    <t>秦律十八种J24</t>
+  </si>
+  <si>
+    <t>承接上简的出库盈亏处理：出库称量粮食，如果粮食数量多出标签记载，多出的粮食要归入官仓。多人共同办理粮食出库的，（原有封存）不必重新改动。未满万石粮堆追加粮食（增积）的规则：秦常规是万石为一个仓储单元。如果现有粮堆还没有满一万石，想要继续往里面添加粮食：如果还是当初负责把这批粮食入仓的官吏来追加粮食，允许直接添加。如果是别的官吏接手来追加粮食，必须先把原有存粮全部称量一遍，核对数量与粮仓题签记录完全相符，才可以把新粮入仓。责任划分：之后这堆粮食出现数量亏欠，就由后来追加粮食的官吏独自承担赔偿责任；并且要把追加粮食官吏的姓名、身份、籍贯，登记在粮仓档案（廥籍）上，留作追责凭证。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J24</t>
+  </si>
+  <si>
+    <t>秦律十八种J25</t>
+  </si>
+  <si>
+    <t>如果是别的官吏，要向原有粮堆追加粮食：必须先称量原先已经存下的粮食，核对实物数量和粮仓题签（题，写清粮食数量的标牌）记载完全吻合，才准许把新粮食入仓堆存。做完这次追加入仓之后，日后该粮堆出现粮食数量不足、亏欠的情况，由后来追加粮食的官吏独自承担赔偿责任。并且要把这次追加粮食官吏的姓名、职务、籍贯，登记在粮仓的专门账簿（廥籍）上面留存备案，作为日后审计追责的凭证。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J25</t>
+  </si>
+  <si>
+    <t>秦律十八种J26</t>
+  </si>
+  <si>
+    <t>这枚仓律简规定已满万石，或是已经开始支取粮食的粮堆，不许再补加粮食，栎阳、咸阳的粮仓分别以二万石、十万石为存储单位，但粮食出入、补粮仍遵照统一律法，相关操作需要长吏共同参与。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J26</t>
+  </si>
+  <si>
+    <t>秦律十八种J27</t>
+  </si>
+  <si>
+    <t>这枚仓律简要求粮食入仓、开仓时要有主管长吏一同到场，如果发现粮食有变质损坏，要另行堆放处理，不能让粮食继续败坏。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J27</t>
+  </si>
+  <si>
+    <t>秦律十八种J28</t>
+  </si>
+  <si>
+    <t>这枚仓律简规定谷物、草料入仓后要即刻登记仓储簿册上报内史，草料一般以万石为一存储单元，咸阳则是二万石，草料的出入仓、追加存储以及核验流程，都参照谷物粮仓的制度执行。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J28</t>
+  </si>
+  <si>
+    <t>秦律十八种J29</t>
+  </si>
+  <si>
+    <t>这枚仓律简规定，谷物、草料的粮堆全部出空时，要把盈余或亏缺情况上报县廷；还未全部出空但已经补齐数额的粮仓，也要向县廷报告，由长吏共同对仓窖加封，粮食出库就要上报相应数目。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J29</t>
+  </si>
+  <si>
+    <t>秦律十八种J30</t>
+  </si>
+  <si>
+    <t>这枚《仓律》简承接上简上报粮仓盈亏的规定，允许县廷根据情况，把邻近粮仓少量粮食归并到同一个县统筹管理；设在都邑的仓窖，粮食出库时依旧要多名官吏共同参与办理。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J30</t>
+  </si>
+  <si>
+    <t>秦律十八种J31</t>
+  </si>
+  <si>
+    <t>这枚仓律简讲粮仓出现粮食亏缺时，要求原任官吏和新任官吏一同把仓内粮食全部出清核查，旧官吏不愿参与的不可强迫；如果原官吏已经不在，就由有秩官吏、令史主持会同仓吏共同清仓，查清粮食亏欠的情况来定责。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J31</t>
+  </si>
+  <si>
+    <t>秦律十八种J32</t>
+  </si>
+  <si>
+    <t>这枚仓律简接续上简粮仓亏空核查的规定，讲由令史会同仓吏共同把仓内粮食全部出清，查清粮食亏欠的情况并论定责任；参与共同核查的官吏不能中途更换，如果中途换人之后才发现粮食不足，就由县令、县丞来承担赔偿亏欠粮食的责任。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J32</t>
+  </si>
+  <si>
+    <t>秦律十八种J33</t>
+  </si>
+  <si>
+    <t>这枚仓律简规定，计量谷子、黍子的时候，要用文书写明粮食的出产年份，分开登记各类粮食的数量，以此作为向人发放口粮的依据。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J33</t>
+  </si>
+  <si>
+    <t>秦律十八种J34</t>
+  </si>
+  <si>
+    <t>这枚仓律简规定统计谷子的时候，要把黄、白、青不同色泽的谷子区分开登记账目，黏谷子（秫）不可以拿来发放给官吏百姓作为口粮。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J34</t>
+  </si>
+  <si>
+    <t>秦律十八种J35</t>
+  </si>
+  <si>
+    <t>这枚仓律简规定，如果稻谷成熟晚于谷子，要把稻谷记到下一年账目；收获上报产量时要区分籼稻、糯稻，专供酿酒的稻米要每年单独储存，不许追加粮食，用来供给外来宾客，到十月要把数量写在文书上报给内史。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J35</t>
+  </si>
+  <si>
+    <t>秦律十八种J36</t>
+  </si>
+  <si>
+    <t>这枚仓律简承接上条，讲各县的太仓要把领取口粮人员的名籍以及相关开销，随同年度账簿一并上报内史，都官机构在年终结账时，需要核对领粮人员的名册。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J36</t>
+  </si>
+  <si>
+    <t>秦律十八种J37</t>
+  </si>
+  <si>
+    <t>这枚仓律简规定各县要把领口粮人员的名籍和粮仓其他开销，随同年度上计账簿一同上报；都官机构在年终核算的时候，要核对领粮人员的名籍。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J37</t>
+  </si>
+  <si>
+    <t>秦律十八种J38</t>
+  </si>
+  <si>
+    <t>这枚仓律简记载了各类农作物每亩的标准播种用种量，稻、麻每亩用二又三分之二斗，谷子、麦子每亩一斗，黍、小豆每亩三分之二斗，大豆每亩半斗；若是肥沃良田，用种量少于这个标准也允许，地里尚有旧茬的，可酌情来确定播种数量。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J38</t>
+  </si>
+  <si>
+    <t>秦律十八种J39</t>
+  </si>
+  <si>
+    <t>这枚仓律简承接上条播种量的条文，讲田里留有作物旧根残茬的地块，播种时要视实际情况斟酌确定用种数量，简末的 “仓” 为《仓律》的篇题标记。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J39</t>
+  </si>
+  <si>
+    <t>秦律十八种J40</t>
+  </si>
+  <si>
+    <t>这枚仓律简规定，各县留作种子的麦子，要参照谷子的标准来储藏保管。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J40</t>
+  </si>
+  <si>
+    <t>秦律十八种J41</t>
+  </si>
+  <si>
+    <t>这枚《仓律》简规定了粮食重量单位与容量单位之间的换算标准，禾黍按重量一石计算，折合带壳粟十六斗又三分之二斗，用来统一官仓粮食计量，方便粮仓统计、发放粮食时换算使用。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J41</t>
+  </si>
+  <si>
+    <t>秦律十八种J42</t>
+  </si>
+  <si>
+    <t>这枚仓律简是发放口粮的相关规定，意思是应当领取粮食的人不来领取，官府就不必给他发放粮食，末尾的 “仓” 为《仓律》篇题标记。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J42</t>
+  </si>
+  <si>
+    <t>秦律十八种J43</t>
+  </si>
+  <si>
+    <t>这枚属于《仓律》的 J43 简，接续 J41 简，记录各类谷物舂米出米率与计量换算标准，二十斗稻谷舂出米十斗，十斗粲米可舂出六斗又三分之二斗的毇米；十斗麦子加工得到三斗麦屑；豆子、小豆、麻十五斗折合为一石；官府发放毇米、粺米这类精米时，直接以十斗算作一石，末尾 “仓” 是篇题标记。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J43</t>
+  </si>
+  <si>
+    <t>秦律十八种J44</t>
+  </si>
+  <si>
+    <t>这枚《仓律》J44 简规定：宦官、都官的官吏与人员奉命为朝廷办事，途经地方时，可由当地县衙垫借口粮；随即发文书通知原本发放该人粮食的县，扣除其口粮额度。如果此人已经在原籍领过口粮，就发文通知现居的县，向本人追还被垫借的粮食，末尾 “仓” 为篇题标记。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J44</t>
+  </si>
+  <si>
+    <t>秦律十八种J45</t>
+  </si>
+  <si>
+    <t>这枚《仓律》J45 简规定：前往军中、到属县办事的人员，应当自己携带口粮，**不可以凭通行符传向当地县的官仓借取粮食**。末尾 “仓” 是《仓律》的篇题标记。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J45</t>
+  </si>
+  <si>
+    <t>秦律十八种J46</t>
+  </si>
+  <si>
+    <t>按月领取口粮的人，如果已经领到当月口粮，之后因公出差，由驿站供给饭食；或是请假归家，到月底仍没有返回，就停发他下一个月初一的口粮，等到本人回来之后，再按归来的日期发放口粮。**有秩级别的官吏不受这条限制，不停发口粮**。末尾 “仓” 为《仓律》篇题标记。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J46</t>
+  </si>
+  <si>
+    <t>秦律十八种J47</t>
+  </si>
+  <si>
+    <t>驾用驿站传马，出行途中喂一次谷物，返程回来再喂一次谷物，这两次饲喂，都以八匹马为一组统一供给饲料。若是马匹被频繁驱使，每日饲喂谷物不得超过一次。如果驾车路途遥远，马匹十分疲劳，可以额外再加喂一次谷物。末尾标注 “仓律”，为该律篇的篇题。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J47</t>
+  </si>
+  <si>
+    <t>秦律十八种J48</t>
+  </si>
+  <si>
+    <t>百姓如果想要借用这类未成年隶妾，官府可以出借；让该隶妾前往百姓家中，由百姓供给她衣食，官府就此停止对这名隶妾的役使。简末标注 “仓律”，为律篇篇题标记。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J48</t>
+  </si>
+  <si>
+    <t>秦律十八种J49</t>
+  </si>
+  <si>
+    <t>隶臣妾为官府服役时，成年隶臣每月发给谷物二石，成年隶妾每月一石半；不参加劳作的，不发放口粮。未成年的小城旦、小隶臣，如果能够劳作，每月谷物一石半；不能劳作的，每月一石。简文还会继续往下延伸，继续规定小隶妾、舂者、婴儿以及从事农业劳作隶臣的口粮标准，并且以身高区分 “大”“小” 徒隶，以此确定劳作与口粮待遇。本简属于《仓律》，是秦官府管控徒隶粮食供给的法律条文。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J49</t>
+  </si>
+  <si>
+    <t>秦律十八种J50</t>
+  </si>
+  <si>
+    <t>能够劳作的小隶妾、小舂（未成年女刑徒），每月发给谷物一石二斗半；还不能劳作的，每月谷物一石。没有母亲的婴儿，官府每月供给谷物半石；即便婴儿尚有母亲，但母亲在官府零散服役，婴儿跟随母亲待在官府的，同样每月发放半石谷物口粮。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J50</t>
+  </si>
+  <si>
+    <t>秦律十八种J51</t>
+  </si>
+  <si>
+    <t>该律文说明农忙田间劳作消耗更大，官府会给务农隶臣增加口粮；同时秦代除年龄外，也用身高来区分徒隶成年、未成年身份，以此确定劳作强度与粮食配给。属于《仓律》徒隶口粮管理制度。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J51</t>
+  </si>
+  <si>
+    <t>秦律十八种J52</t>
+  </si>
+  <si>
+    <t>秦代徒隶不完全凭年龄，**以身高作为重要判定标准**，五尺二寸是最低劳作门槛，达到该身高就必须服役；六尺五寸（男）、六尺二寸（女）是成年与未成年徒隶的分界，用来确定口粮额度与劳动强度。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J52</t>
+  </si>
+  <si>
+    <t>秦律十八种J53</t>
+  </si>
+  <si>
+    <t>未成年的小隶臣妾，在八月办理登记（傅），正式转为大隶臣妾（成年徒隶），但是口粮标准并不立刻上调，要等到十月才开始增加口粮。末尾 “仓” 是《仓律》篇题标记。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J53</t>
+  </si>
+  <si>
+    <t>秦律十八种J54</t>
+  </si>
+  <si>
+    <t>官府要汇总统计零散服役（总冗）的隶臣妾，登记他们的出勤劳作天数，据此核算、发放口粮；如果有逃亡的徒隶，要立刻停止供给其口粮。末尾 “仓” 为《仓律》篇题标记。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J54</t>
+  </si>
+  <si>
+    <t>秦律十八种J55</t>
+  </si>
+  <si>
+    <t>城旦从事筑墙，或是其他劳动强度与筑墙相当的重体力劳作，每日两餐：早饭半斗，晚饭三分之一斗（旦半夕参）。如果是值守官署、做一般轻活，早晚两餐都供给三分之一斗（参食之）。刑徒生病，口粮要酌情裁定发放，由主管官吏负责处置。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J55</t>
+  </si>
+  <si>
+    <t>秦律十八种J56</t>
+  </si>
+  <si>
+    <t>如果她们从事土工类重体力劳作，执行 “参食之”，即早、晚两餐各发放三分之一斗口粮。如果不从事土工重活，就依照原有法律条文的标准供给口粮。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J56</t>
+  </si>
+  <si>
+    <t>秦律十八种J57</t>
+  </si>
+  <si>
+    <t>城旦按日供给口粮；到月末结算，剩余粮食归入后九月（闰九月）的口粮储备。如果城旦从事轻松的劳作（安事），却违规增加口粮，主管官吏要按照 “犯令” 的律令予以惩处。城旦、舂这类刑徒，当月服役时间不足整月，要相应扣减口粮。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J57</t>
+  </si>
+  <si>
+    <t>秦律十八种J58</t>
+  </si>
+  <si>
+    <t>城旦、舂这类刑徒，如果当月实际服役时间不足整个月份（月不盈），官府要按照实际出勤天数扣减口粮；末尾 “仓” 是《仓律》的篇题标记。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J58</t>
+  </si>
+  <si>
+    <t>秦律十八种J59</t>
+  </si>
+  <si>
+    <t>免隶臣妾、隶臣妾，如果做筑墙，或是劳动强度和筑墙相当的重活：男子：早饭半斗，晚饭三分之一斗（旦半夕参）；女子：早晚两餐各三分之一斗（参）。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J59</t>
+  </si>
+  <si>
+    <t>秦律十八种J60</t>
+  </si>
+  <si>
+    <t>对于被拘押的受罚囚徒（𩚚囚），官府每日供给口粮标准为**少半斗（三分之一斗）**。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J60</t>
+  </si>
+  <si>
+    <t>秦律十八种J61</t>
+  </si>
+  <si>
+    <t>普通隶臣想要赎免自身，需要交付两名壮年男子替代官府劳作，官府允许赎免。已到免老年龄的老年隶臣、身高五尺以下的小隶臣，以及隶妾，赎免只需要交付一名壮年男子即可。用来顶替赎身的人必须是男子，顶替者本人将成为隶臣。从事文绣、女红、缝制衣物这类官府手工业的女子隶妾，不允许赎免。如果隶臣妾原籍在边县，赎免之后，要把户籍重新登记回原籍所在的县。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J61</t>
+  </si>
+  <si>
+    <t>秦律十八种J62</t>
+  </si>
+  <si>
+    <t>拿来充当赎身替代者的，必须是男子；这名顶替的男子，自身就变为隶臣。从事文绣、女红、缝制衣物的女隶妾，不允许赎免，官府要保留这批手工业技术劳动力。如果被赎免的隶臣妾原籍在边县，赎免之后，要在原籍县重新登记户籍名数（复数其县），恢复普通百姓户籍身份。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J62</t>
+  </si>
+  <si>
+    <t>秦律十八种J63</t>
+  </si>
+  <si>
+    <t>官府养鸡，要设置在远离粮仓的地方，防止鸡损耗官仓粮食。官仓如果需要养狗捕鼠护粮，养狗的数量只以够用为限度，不许多养。官养的猪、鸡繁育出小猪、小鸡，如果官府不需要留用，应当将其变卖；卖得的钱款要单独记账，不能和其他仓府财物混在一起核算。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J63</t>
+  </si>
+  <si>
+    <t>秦律十八种J64</t>
+  </si>
+  <si>
+    <t>官府收纳钱币，每一千枚铜钱装入一个畚（草编容器），加盖县令、县丞的印章封缄。就算钱币不足一千枚，同样也要加盖印章封存。收纳钱币时，质量好的钱币与质量差的钱币要混合装在一起，不得挑拣分开。官府要支出现钱的时候，先要把封存的畚呈交给令、丞核验封泥，确认完好之后，才可以启封取用。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J64</t>
+  </si>
+  <si>
+    <t>秦律十八种J65</t>
+  </si>
+  <si>
+    <t>百姓在市场交易使用铜钱时，好钱、劣钱必须混杂流通，不允许只挑选好钱、拒收劣质钱币。</t>
+  </si>
+  <si>
+    <t>http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J65</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +2025,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1343,9 +2049,6 @@
     </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1661,7 +2364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2001,7 +2704,7 @@
       <c r="A31" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D31" s="3" t="s">
@@ -2028,6 +2731,848 @@
       </c>
       <c r="D33" s="2" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="B35" s="8"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="B36" s="8"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>124</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>133</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>136</v>
+      </c>
+      <c r="B50" t="s">
+        <v>137</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>139</v>
+      </c>
+      <c r="B51" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>142</v>
+      </c>
+      <c r="B52" t="s">
+        <v>143</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" t="s">
+        <v>146</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>148</v>
+      </c>
+      <c r="B54" t="s">
+        <v>149</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>151</v>
+      </c>
+      <c r="B55" t="s">
+        <v>152</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>154</v>
+      </c>
+      <c r="B56" t="s">
+        <v>155</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>157</v>
+      </c>
+      <c r="B57" t="s">
+        <v>158</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>160</v>
+      </c>
+      <c r="B58" t="s">
+        <v>161</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>163</v>
+      </c>
+      <c r="B59" t="s">
+        <v>164</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>166</v>
+      </c>
+      <c r="B60" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>169</v>
+      </c>
+      <c r="B61" t="s">
+        <v>170</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>172</v>
+      </c>
+      <c r="B62" t="s">
+        <v>173</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>175</v>
+      </c>
+      <c r="B63" t="s">
+        <v>176</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>178</v>
+      </c>
+      <c r="B64" t="s">
+        <v>179</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>181</v>
+      </c>
+      <c r="B65" t="s">
+        <v>182</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>184</v>
+      </c>
+      <c r="B66" t="s">
+        <v>185</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>187</v>
+      </c>
+      <c r="B67" t="s">
+        <v>188</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>190</v>
+      </c>
+      <c r="B68" t="s">
+        <v>191</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>193</v>
+      </c>
+      <c r="B69" t="s">
+        <v>194</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>196</v>
+      </c>
+      <c r="B70" t="s">
+        <v>197</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>199</v>
+      </c>
+      <c r="B71" t="s">
+        <v>200</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>202</v>
+      </c>
+      <c r="B72" t="s">
+        <v>203</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>205</v>
+      </c>
+      <c r="B73" t="s">
+        <v>206</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>208</v>
+      </c>
+      <c r="B74" t="s">
+        <v>209</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>211</v>
+      </c>
+      <c r="B75" t="s">
+        <v>212</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>214</v>
+      </c>
+      <c r="B76" t="s">
+        <v>215</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>217</v>
+      </c>
+      <c r="B77" t="s">
+        <v>218</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>220</v>
+      </c>
+      <c r="B78" t="s">
+        <v>221</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>223</v>
+      </c>
+      <c r="B79" t="s">
+        <v>224</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>226</v>
+      </c>
+      <c r="B80" t="s">
+        <v>227</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>229</v>
+      </c>
+      <c r="B81" t="s">
+        <v>230</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>232</v>
+      </c>
+      <c r="B82" t="s">
+        <v>233</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>235</v>
+      </c>
+      <c r="B83" t="s">
+        <v>236</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>238</v>
+      </c>
+      <c r="B84" t="s">
+        <v>239</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>241</v>
+      </c>
+      <c r="B85" t="s">
+        <v>242</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>244</v>
+      </c>
+      <c r="B86" t="s">
+        <v>245</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>247</v>
+      </c>
+      <c r="B87" t="s">
+        <v>248</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>250</v>
+      </c>
+      <c r="B88" t="s">
+        <v>251</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>253</v>
+      </c>
+      <c r="B89" t="s">
+        <v>254</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>256</v>
+      </c>
+      <c r="B90" t="s">
+        <v>257</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>259</v>
+      </c>
+      <c r="B91" t="s">
+        <v>260</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>262</v>
+      </c>
+      <c r="B92" t="s">
+        <v>263</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>265</v>
+      </c>
+      <c r="B93" t="s">
+        <v>266</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>268</v>
+      </c>
+      <c r="B94" t="s">
+        <v>269</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>271</v>
+      </c>
+      <c r="B95" t="s">
+        <v>272</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>274</v>
+      </c>
+      <c r="B96" t="s">
+        <v>275</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>277</v>
+      </c>
+      <c r="B97" t="s">
+        <v>278</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>280</v>
+      </c>
+      <c r="B98" t="s">
+        <v>281</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>283</v>
+      </c>
+      <c r="B99" t="s">
+        <v>284</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>286</v>
+      </c>
+      <c r="B100" t="s">
+        <v>287</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>289</v>
+      </c>
+      <c r="B101" t="s">
+        <v>290</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>292</v>
+      </c>
+      <c r="B102" t="s">
+        <v>293</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>295</v>
+      </c>
+      <c r="B103" t="s">
+        <v>296</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>298</v>
+      </c>
+      <c r="B104" t="s">
+        <v>299</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>301</v>
+      </c>
+      <c r="B105" t="s">
+        <v>302</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>304</v>
+      </c>
+      <c r="B106" t="s">
+        <v>305</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>307</v>
+      </c>
+      <c r="B107" t="s">
+        <v>308</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
+        <v>310</v>
+      </c>
+      <c r="B108" t="s">
+        <v>311</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
+        <v>313</v>
+      </c>
+      <c r="B109" t="s">
+        <v>314</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>316</v>
+      </c>
+      <c r="B110" t="s">
+        <v>317</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>319</v>
+      </c>
+      <c r="B111" t="s">
+        <v>320</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -2044,6 +3589,82 @@
     <hyperlink ref="D31" r:id="rId10" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J1"/>
     <hyperlink ref="D32" r:id="rId11" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J2" tooltip="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J2"/>
     <hyperlink ref="D33" r:id="rId12" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J3"/>
+    <hyperlink ref="D34" r:id="rId13" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J4" tooltip="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J4"/>
+    <hyperlink ref="D37" r:id="rId14" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J5"/>
+    <hyperlink ref="D38" r:id="rId15" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J6"/>
+    <hyperlink ref="D39" r:id="rId16" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J7"/>
+    <hyperlink ref="D40" r:id="rId17" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J8"/>
+    <hyperlink ref="D41" r:id="rId18" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J9"/>
+    <hyperlink ref="D42" r:id="rId19" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J10"/>
+    <hyperlink ref="D43" r:id="rId20" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J11"/>
+    <hyperlink ref="D44" r:id="rId21" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J12"/>
+    <hyperlink ref="D45" r:id="rId22" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J13"/>
+    <hyperlink ref="D46" r:id="rId23" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=2%E8%AA%9E%E6%9B%B8&amp;jian=J14"/>
+    <hyperlink ref="D47" r:id="rId24" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J1"/>
+    <hyperlink ref="D48" r:id="rId25" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J2"/>
+    <hyperlink ref="D49" r:id="rId26" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J3"/>
+    <hyperlink ref="D50" r:id="rId27" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J4"/>
+    <hyperlink ref="D51" r:id="rId28" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J5"/>
+    <hyperlink ref="D52" r:id="rId29" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J6"/>
+    <hyperlink ref="D53" r:id="rId30" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J7"/>
+    <hyperlink ref="D54" r:id="rId31" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J8"/>
+    <hyperlink ref="D55" r:id="rId32" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J9"/>
+    <hyperlink ref="D56" r:id="rId33" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J10"/>
+    <hyperlink ref="D57" r:id="rId34" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J11"/>
+    <hyperlink ref="D58" r:id="rId35" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J12"/>
+    <hyperlink ref="D59" r:id="rId36" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J13"/>
+    <hyperlink ref="D60" r:id="rId37" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J14"/>
+    <hyperlink ref="D61" r:id="rId38" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J15"/>
+    <hyperlink ref="D62" r:id="rId39" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J16"/>
+    <hyperlink ref="D63" r:id="rId40" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J17"/>
+    <hyperlink ref="D64" r:id="rId41" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J18"/>
+    <hyperlink ref="D65" r:id="rId42" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J19"/>
+    <hyperlink ref="D66" r:id="rId43" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J20"/>
+    <hyperlink ref="D67" r:id="rId44" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J21"/>
+    <hyperlink ref="D68" r:id="rId45" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J22"/>
+    <hyperlink ref="D69" r:id="rId46" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J23"/>
+    <hyperlink ref="D70" r:id="rId47" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J24"/>
+    <hyperlink ref="D71" r:id="rId48" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J25"/>
+    <hyperlink ref="D72" r:id="rId49" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J26"/>
+    <hyperlink ref="D73" r:id="rId50" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J27"/>
+    <hyperlink ref="D74" r:id="rId51" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J28"/>
+    <hyperlink ref="D75" r:id="rId52" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J29"/>
+    <hyperlink ref="D76" r:id="rId53" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J30"/>
+    <hyperlink ref="D77" r:id="rId54" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J31"/>
+    <hyperlink ref="D78" r:id="rId55" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J32"/>
+    <hyperlink ref="D79" r:id="rId56" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J33"/>
+    <hyperlink ref="D80" r:id="rId57" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J34"/>
+    <hyperlink ref="D81" r:id="rId58" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J35"/>
+    <hyperlink ref="D82" r:id="rId59" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J36"/>
+    <hyperlink ref="D83" r:id="rId60" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J37"/>
+    <hyperlink ref="D84" r:id="rId61" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J38"/>
+    <hyperlink ref="D85" r:id="rId62" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J39"/>
+    <hyperlink ref="D86" r:id="rId63" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J40"/>
+    <hyperlink ref="D87" r:id="rId64" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J41"/>
+    <hyperlink ref="D88" r:id="rId65" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J42"/>
+    <hyperlink ref="D89" r:id="rId66" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J43"/>
+    <hyperlink ref="D90" r:id="rId67" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J44"/>
+    <hyperlink ref="D91" r:id="rId68" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J45"/>
+    <hyperlink ref="D92" r:id="rId69" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J46"/>
+    <hyperlink ref="D93" r:id="rId70" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J47"/>
+    <hyperlink ref="D94" r:id="rId71" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J48"/>
+    <hyperlink ref="D95" r:id="rId72" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J49"/>
+    <hyperlink ref="D96" r:id="rId73" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J50"/>
+    <hyperlink ref="D97" r:id="rId74" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J51"/>
+    <hyperlink ref="D98" r:id="rId75" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J52"/>
+    <hyperlink ref="D99" r:id="rId76" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J53"/>
+    <hyperlink ref="D100" r:id="rId77" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J54"/>
+    <hyperlink ref="D101" r:id="rId78" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J55"/>
+    <hyperlink ref="D102" r:id="rId79" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J56"/>
+    <hyperlink ref="D103" r:id="rId80" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J57"/>
+    <hyperlink ref="D104" r:id="rId81" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J58"/>
+    <hyperlink ref="D105" r:id="rId82" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J59"/>
+    <hyperlink ref="D106" r:id="rId83" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J60"/>
+    <hyperlink ref="D107" r:id="rId84" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J61"/>
+    <hyperlink ref="D108" r:id="rId85" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J62"/>
+    <hyperlink ref="D109" r:id="rId86" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J63"/>
+    <hyperlink ref="D110" r:id="rId87" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J64"/>
+    <hyperlink ref="D111" r:id="rId88" display="http://www.kaom.net/jianq88.php?book=%E7%9D%A1%E8%99%8E%E5%9C%B0%E7%B0%A1&amp;pian=3%E7%A7%A6%E5%BE%8B%E5%8D%81%E5%85%AB%E7%A8%AE&amp;jian=J65"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
